--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.92721715652736</v>
+        <v>6.163172787935696</v>
       </c>
       <c r="D2" t="n">
-        <v>38.11179313403103</v>
+        <v>6.193166384280043</v>
       </c>
       <c r="E2" t="n">
-        <v>6.15839268105163</v>
+        <v>1.00073881067089</v>
       </c>
       <c r="F2" t="n">
-        <v>6.342972928252943</v>
+        <v>1.030733100841104</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.70264308427615</v>
+        <v>5.639179501194875</v>
       </c>
       <c r="D3" t="n">
-        <v>35.0272163145327</v>
+        <v>5.691922651111565</v>
       </c>
       <c r="E3" t="n">
-        <v>6.15839268105163</v>
+        <v>1.00073881067089</v>
       </c>
       <c r="F3" t="n">
-        <v>6.342972928252943</v>
+        <v>1.030733100841104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.13342794607491</v>
+        <v>3.434182041237174</v>
       </c>
       <c r="D4" t="n">
-        <v>20.72009920991717</v>
+        <v>3.367016121611541</v>
       </c>
       <c r="E4" t="n">
-        <v>6.15839268105163</v>
+        <v>1.00073881067089</v>
       </c>
       <c r="F4" t="n">
-        <v>6.342972928252943</v>
+        <v>1.030733100841104</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.25466054034002</v>
+        <v>4.753882337805254</v>
       </c>
       <c r="D5" t="n">
-        <v>29.0180227810415</v>
+        <v>4.715428701919244</v>
       </c>
       <c r="E5" t="n">
-        <v>6.15839268105163</v>
+        <v>1.00073881067089</v>
       </c>
       <c r="F5" t="n">
-        <v>6.342972928252943</v>
+        <v>1.030733100841104</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.64714691423632</v>
+        <v>5.955161373563403</v>
       </c>
       <c r="D6" t="n">
-        <v>36.31850931516782</v>
+        <v>5.90175776371477</v>
       </c>
       <c r="E6" t="n">
-        <v>6.15839268105163</v>
+        <v>1.00073881067089</v>
       </c>
       <c r="F6" t="n">
-        <v>6.342972928252943</v>
+        <v>1.030733100841104</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
